--- a/data/trans_dic/P1435-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1435-Habitat-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,72</t>
+          <t>2,81; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,06</t>
+          <t>2,25; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,31</t>
+          <t>0,62; 2,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,14</t>
+          <t>2,88; 6,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,72</t>
+          <t>2,81; 5,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,06</t>
+          <t>2,25; 5,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,31</t>
+          <t>0,62; 2,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,14</t>
+          <t>2,88; 6,2</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,51</t>
+          <t>3,7; 6,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,68</t>
+          <t>2,41; 4,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,71</t>
+          <t>0,53; 1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,04</t>
+          <t>4,31; 6,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,51</t>
+          <t>3,7; 6,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,68</t>
+          <t>2,41; 4,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,71</t>
+          <t>0,53; 1,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,04</t>
+          <t>4,31; 6,92</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,62</t>
+          <t>9,67; 14,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,39</t>
+          <t>4,06; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,74</t>
+          <t>0,98; 2,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,48</t>
+          <t>6,45; 10,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,62</t>
+          <t>9,67; 14,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,39</t>
+          <t>4,06; 7,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,74</t>
+          <t>0,98; 2,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,48</t>
+          <t>6,45; 10,75</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,89</t>
+          <t>8,03; 11,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,82</t>
+          <t>2,43; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,45</t>
+          <t>2,25; 4,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 30,32</t>
+          <t>4,99; 7,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,89</t>
+          <t>8,03; 11,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,82</t>
+          <t>2,43; 4,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,45</t>
+          <t>2,25; 4,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 30,32</t>
+          <t>4,99; 7,87</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>31424</t>
         </is>
       </c>
     </row>
@@ -1332,42 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19104; 39371</t>
+          <t>19374; 39323</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15820; 35250</t>
+          <t>15705; 35287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4218; 15547</t>
+          <t>4159; 15863</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19860; 41461</t>
+          <t>21134; 45448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19104; 39371</t>
+          <t>19374; 39323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15820; 35250</t>
+          <t>15705; 35287</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4218; 15547</t>
+          <t>4159; 15863</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19860; 41461</t>
+          <t>21134; 45448</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58544</t>
         </is>
       </c>
     </row>
@@ -1480,42 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36319; 63077</t>
+          <t>35836; 64666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23798; 48111</t>
+          <t>24849; 47825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5507; 17862</t>
+          <t>5510; 18341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40478; 67201</t>
+          <t>45980; 73882</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36319; 63077</t>
+          <t>35836; 64666</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23798; 48111</t>
+          <t>24849; 47825</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5507; 17862</t>
+          <t>5510; 18341</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40478; 67201</t>
+          <t>45980; 73882</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>68492</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66546; 99958</t>
+          <t>66098; 98739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31556; 57459</t>
+          <t>31526; 57512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6774; 21518</t>
+          <t>7680; 21933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27480; 78840</t>
+          <t>52117; 86864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66546; 99958</t>
+          <t>66098; 98739</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31556; 57459</t>
+          <t>31526; 57512</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6774; 21518</t>
+          <t>7680; 21933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27480; 78840</t>
+          <t>52117; 86864</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>70473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>70473</t>
         </is>
       </c>
     </row>
@@ -1776,42 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84883; 123458</t>
+          <t>83378; 120444</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25655; 50707</t>
+          <t>25603; 50005</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23644; 46407</t>
+          <t>23474; 47448</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61349; 330793</t>
+          <t>55706; 87768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84883; 123458</t>
+          <t>83378; 120444</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25655; 50707</t>
+          <t>25603; 50005</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23644; 46407</t>
+          <t>23474; 47448</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61349; 330793</t>
+          <t>55706; 87768</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
     </row>
@@ -1924,42 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
     </row>
